--- a/administrative_forms/009_task_progress_monitoring_form--administrative_forms.xlsx
+++ b/administrative_forms/009_task_progress_monitoring_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,64 +520,64 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>task_progress_form_1</t>
+          <t>task_id</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Task ID</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>task_progress_form_2</t>
+          <t>task_description</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Task Description</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>task_progress_form_3</t>
+          <t>task_is_completed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Is the task completed?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>task_progress_form_4</t>
+          <t>task_completion_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Date of completion</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>task_progress_form_5</t>
+          <t>task_completion_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Time of completion</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>task_progress_form_6</t>
+          <t>task_completion_status</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Task completion status</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>task_progress_form_7</t>
+          <t>task_is_urgent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Is the task urgent?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>task_progress_form_8</t>
+          <t>task_status_progress</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Task status progress</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,23 +699,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>task_progress_form_9</t>
+          <t>task_is_completed_successfully</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Is the task completed successfully?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,35 +727,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>task_progress_form_10</t>
+          <t>task_priority</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Task priority</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>task_progress_form_11</t>
+          <t>task_completion_date_milestone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Completion date for milestone 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>task_progress_form_12</t>
+          <t>task_completion_date_milestone_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Completion date for milestone 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>task_progress_form_13</t>
+          <t>task_progress_percentage</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Task progress in percentage</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>task_progress_form_14</t>
+          <t>task_progress_reason_delayed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Reason for delay</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>task_progress_form_15</t>
+          <t>task_progress_status</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Task progress status</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>task_progress_form_16</t>
+          <t>task_progress_date</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Estimated completion date</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>task_progress_form_17</t>
+          <t>task_actual_completion_date</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Actual completion date</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,85 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>task_progress_form_18</t>
+          <t>task_progress_percentage_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Task progress percentage</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>task_progress_form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>task_progress_form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>task_progress_form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1006,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1034,126 +965,126 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>task_progress_form_2_choices</t>
+          <t>task_is_completed_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>task_progress_form_2_choices</t>
+          <t>task_is_completed_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>task_progress_form_2_choices</t>
+          <t>task_completion_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>task_progress_form_6_choices</t>
+          <t>task_completion_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>task_progress_form_6_choices</t>
+          <t>task_completion_status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>task_progress_form_7_choices</t>
+          <t>task_is_urgent_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>task_progress_form_7_choices</t>
+          <t>task_is_urgent_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>task_progress_form_9_choices</t>
+          <t>task_status_progress_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1170,7 +1101,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>task_progress_form_9_choices</t>
+          <t>task_status_progress_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1187,34 +1118,153 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>task_progress_form_10_choices</t>
+          <t>task_status_progress_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>task_progress_form_10_choices</t>
+          <t>task_is_completed_successfully_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>task_is_completed_successfully_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>task_priority_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>task_priority_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>task_priority_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>task_progress_status_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>task_progress_status_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>task_progress_status_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
